--- a/artfynd/A 40924-2022 artfynd.xlsx
+++ b/artfynd/A 40924-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40924-2022 artfynd.xlsx
+++ b/artfynd/A 40924-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>93281092</v>
       </c>
       <c r="B2" t="n">
-        <v>57482</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på determinatörs verifiering</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -736,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567753.2609454885</v>
+        <v>567753</v>
       </c>
       <c r="R2" t="n">
-        <v>6432168.381466581</v>
+        <v>6432169</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
